--- a/data/gravel/Megamo Jakar 2025.xlsx
+++ b/data/gravel/Megamo Jakar 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10824"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C1B8D23-5FFE-CD47-89C9-F98757E36266}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{772FFE15-59E6-DF4E-89DA-7C9A0BFF79B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="29480" yWindow="-18460" windowWidth="29380" windowHeight="17980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="142">
   <si>
     <t>brand</t>
   </si>
@@ -456,6 +456,9 @@
   </si>
   <si>
     <t>a8:g36</t>
+  </si>
+  <si>
+    <t>https://www.megamo.com/biblioteca/arxius/MY26/JAKAR/images/JAKAR-20_CORAL26.png</t>
   </si>
 </sst>
 </file>
@@ -878,6 +881,9 @@
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="B6" s="1" t="s">
+        <v>141</v>
+      </c>
       <c r="C6" s="3"/>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>

--- a/data/gravel/Megamo Jakar 2025.xlsx
+++ b/data/gravel/Megamo Jakar 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{772FFE15-59E6-DF4E-89DA-7C9A0BFF79B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73C9FD1A-5411-544A-A0E9-C2C4C80ECCE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29480" yWindow="-18460" windowWidth="29380" windowHeight="17980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10660" yWindow="860" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="144">
   <si>
     <t>brand</t>
   </si>
@@ -332,9 +332,6 @@
     <t>Megamo</t>
   </si>
   <si>
-    <t>euro</t>
-  </si>
-  <si>
     <t>73º</t>
   </si>
   <si>
@@ -459,6 +456,15 @@
   </si>
   <si>
     <t>https://www.megamo.com/biblioteca/arxius/MY26/JAKAR/images/JAKAR-20_CORAL26.png</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Girona, Spain</t>
+  </si>
+  <si>
+    <t>EUR</t>
   </si>
 </sst>
 </file>
@@ -833,7 +839,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q76"/>
+  <dimension ref="A1:Q77"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" style="1" customWidth="1"/>
@@ -853,7 +859,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.3">
@@ -877,12 +883,12 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B6" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C6" s="3"/>
       <c r="D6" s="3"/>
@@ -921,7 +927,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
@@ -960,7 +966,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>83</v>
@@ -999,10 +1005,10 @@
         <v>529</v>
       </c>
       <c r="P8" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="Q8" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.3">
@@ -1049,7 +1055,7 @@
         <v>550</v>
       </c>
       <c r="P9" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="Q9" s="1" t="s">
         <v>97</v>
@@ -1102,7 +1108,7 @@
         <v>95</v>
       </c>
       <c r="Q10" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.3">
@@ -1152,7 +1158,7 @@
         <v>95</v>
       </c>
       <c r="Q11" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.3">
@@ -1202,7 +1208,7 @@
         <v>95</v>
       </c>
       <c r="Q12" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.3">
@@ -1251,7 +1257,7 @@
         <v>632</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.3">
@@ -1277,7 +1283,7 @@
         <v>71</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="J15" s="1" t="s">
         <v>83</v>
@@ -1318,7 +1324,7 @@
         <v>73</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="J16" s="1">
         <v>529</v>
@@ -1341,7 +1347,7 @@
         <v>13</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C17" s="1">
         <v>70</v>
@@ -1359,7 +1365,7 @@
         <v>70</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="J17" s="1">
         <v>347</v>
@@ -1379,10 +1385,10 @@
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C18" s="1">
         <v>286</v>
@@ -1400,30 +1406,30 @@
         <v>286</v>
       </c>
       <c r="I18" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="J18" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="J18" s="1" t="s">
+      <c r="K18" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="K18" s="1" t="s">
+      <c r="L18" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="M18" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="L18" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="M18" s="1" t="s">
+      <c r="N18" s="1" t="s">
         <v>115</v>
-      </c>
-      <c r="N18" s="1" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C19" s="4">
         <v>572</v>
@@ -1441,7 +1447,7 @@
         <v>657</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="J19" s="1">
         <v>415</v>
@@ -1464,7 +1470,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C20" s="1">
         <v>992</v>
@@ -1482,7 +1488,7 @@
         <v>1078</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="J20" s="1">
         <v>494</v>
@@ -1505,7 +1511,7 @@
         <v>18</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C21" s="1">
         <v>45</v>
@@ -1524,7 +1530,7 @@
       </c>
       <c r="H21" s="7"/>
       <c r="I21" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J21" s="1">
         <v>15.7</v>
@@ -1547,7 +1553,7 @@
         <v>71</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C22" s="1">
         <v>81.7</v>
@@ -1565,7 +1571,7 @@
         <v>75</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="J22" s="1">
         <v>70</v>
@@ -1585,10 +1591,10 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C23" s="1">
         <v>76.8</v>
@@ -1606,7 +1612,7 @@
         <v>70.900000000000006</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="J23" s="1">
         <v>74.5</v>
@@ -1630,7 +1636,7 @@
       </c>
       <c r="B24" s="6"/>
       <c r="I24" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="J24" s="1">
         <v>105</v>
@@ -1659,7 +1665,7 @@
       <c r="F25" s="7"/>
       <c r="G25" s="7"/>
       <c r="I25" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="J25" s="1">
         <v>70</v>
@@ -1682,7 +1688,7 @@
         <v>19</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="J26" s="1">
         <v>286</v>
@@ -1705,7 +1711,7 @@
         <v>20</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="J27" s="1">
         <v>430</v>
@@ -1744,7 +1750,7 @@
       </c>
       <c r="H28" s="4"/>
       <c r="I28" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="J28" s="4">
         <v>424.3</v>
@@ -1768,7 +1774,7 @@
       </c>
       <c r="H29" s="4"/>
       <c r="I29" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="J29" s="4">
         <v>572</v>
@@ -1806,7 +1812,7 @@
         <v>700</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="J30" s="1">
         <v>567.70000000000005</v>
@@ -1844,7 +1850,7 @@
         <v>45</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="J31" s="1">
         <v>992</v>
@@ -1882,7 +1888,7 @@
         <v>50</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="J32" s="1">
         <v>45</v>
@@ -1925,7 +1931,7 @@
         <v>190</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="J33" s="1">
         <v>81.7</v>
@@ -1968,7 +1974,7 @@
         <v>210</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="J34" s="1">
         <v>76.8</v>
@@ -2006,7 +2012,7 @@
         <v>190</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="J35" s="1">
         <v>26.3</v>
@@ -2045,7 +2051,7 @@
       </c>
       <c r="H36" s="4"/>
       <c r="I36" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="J36" s="1">
         <v>46</v>
@@ -2066,7 +2072,7 @@
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="E37" s="8"/>
       <c r="I37" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="J37" s="1">
         <v>116</v>
@@ -2126,7 +2132,7 @@
         <v>31</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.3">
@@ -2306,7 +2312,15 @@
         <v>65</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>99</v>
+        <v>143</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>142</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Megamo Jakar 2025.xlsx
+++ b/data/gravel/Megamo Jakar 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73C9FD1A-5411-544A-A0E9-C2C4C80ECCE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D45D5393-D193-974E-BCEE-54ADF85C7CE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10660" yWindow="860" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="150">
   <si>
     <t>brand</t>
   </si>
@@ -465,6 +465,24 @@
   </si>
   <si>
     <t>EUR</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -839,7 +857,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q77"/>
+  <dimension ref="A1:Q83"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" style="1" customWidth="1"/>
@@ -2194,132 +2212,162 @@
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
-        <v>42</v>
+        <v>144</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
-        <v>43</v>
+        <v>145</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
-        <v>44</v>
+        <v>146</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
-        <v>45</v>
+        <v>147</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
-        <v>46</v>
+        <v>148</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
-        <v>47</v>
+        <v>149</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A65" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A66" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A67" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A68" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A69" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A70" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A65" s="1" t="s">
+    <row r="71" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A71" s="1" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A66" s="1" t="s">
+    <row r="72" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A72" s="1" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A67" s="1" t="s">
+    <row r="73" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A73" s="1" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A68" s="1" t="s">
+    <row r="74" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A74" s="1" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A69" s="1" t="s">
+    <row r="75" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A75" s="1" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A70" s="1" t="s">
+    <row r="76" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A76" s="1" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A71" s="1" t="s">
+    <row r="77" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A77" s="1" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A72" s="1" t="s">
+    <row r="78" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A78" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A73" s="1" t="s">
+    <row r="79" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A79" s="1" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A74" s="1" t="s">
+    <row r="80" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A80" s="1" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A75" s="1" t="s">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A81" s="1" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A76" s="1" t="s">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A82" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B76" s="1" t="s">
+      <c r="B82" s="1" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A77" s="1" t="s">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A83" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="B77" s="1" t="s">
+      <c r="B83" s="1" t="s">
         <v>142</v>
       </c>
     </row>

--- a/data/gravel/Megamo Jakar 2025.xlsx
+++ b/data/gravel/Megamo Jakar 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11214"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D45D5393-D193-974E-BCEE-54ADF85C7CE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4110F2C9-09A5-BF47-9832-7676DB7CE92B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2167,6 +2167,9 @@
       <c r="A45" s="1" t="s">
         <v>34</v>
       </c>
+      <c r="B45" s="1">
+        <v>50</v>
+      </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
